--- a/projects/psmmc-dashboard/tests/fixtures/po-basic.xlsx
+++ b/projects/psmmc-dashboard/tests/fixtures/po-basic.xlsx
@@ -418,7 +418,7 @@
         <v>5000001</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-12</v>
+        <v>2026-06-13</v>
       </c>
       <c r="C2">
         <v>500</v>
